--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260907.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>437,358,478</t>
+          <t>253,316,410</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>253,316,410</t>
+          <t>437,358,478</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>107,174,490</t>
+          <t>25,287,024</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>25,287,024</t>
+          <t>107,174,490</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
